--- a/docs/oc-regiones/gas-licuado-de-petroleo/antofagasta.xlsx
+++ b/docs/oc-regiones/gas-licuado-de-petroleo/antofagasta.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1157.21</v>
+        <v>1147.41</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>106.83</v>
+        <v>106.28</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>63.91</v>
+        <v>63.58</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1153.19</v>
+        <v>1141.11</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>3205.84</v>
+        <v>3172.26</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>9402.559999999999</v>
+        <v>9351.16</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>5460.04</v>
+        <v>5430.19</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>3764.15</v>
+        <v>3743.58</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>6927.27</v>
+        <v>6889.41</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>889.65</v>
+        <v>884.78</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>7880.73</v>
+        <v>7837.57</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>466.74</v>
+        <v>464.19</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>7039.87</v>
+        <v>7001.32</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1021.24</v>
+        <v>1024.6</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>6361.41</v>
+        <v>6407.27</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>6246.73</v>
+        <v>6235.65</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>3138.72</v>
+        <v>3125.79</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>547.88</v>
+        <v>547.03</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2282.84</v>
+        <v>2294.63</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>141.84</v>
+        <v>140.01</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>494.28</v>
+        <v>487.89</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>6415.37</v>
+        <v>6333.88</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>432.21</v>
+        <v>426.72</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>294.69</v>
+        <v>291.75</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>141.84</v>
+        <v>141.33</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>435.96</v>
+        <v>435.02</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>19571.76</v>
+        <v>19489.71</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>3992.34</v>
+        <v>3946.14</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2262.95</v>
+        <v>2236.76</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>426.26</v>
+        <v>421.33</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>366.81</v>
+        <v>368.47</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>550.21</v>
+        <v>551.67</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1340.98</v>
+        <v>1339.1</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>6047.37</v>
+        <v>6055.12</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>17909.76</v>
+        <v>18101.87</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1409.3</v>
+        <v>1424.42</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>136.38</v>
+        <v>138.06</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>6174.5</v>
+        <v>6054.07</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>5502.48</v>
+        <v>5431.36</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>4853.24</v>
+        <v>4790.51</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>48133.87</v>
+        <v>47968.67</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>4914.25</v>
+        <v>4883.46</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>6563.95</v>
+        <v>6522.81</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>947.73</v>
+        <v>962.16</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>463.09</v>
+        <v>470.15</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>4760.32</v>
+        <v>4876.08</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>701.78</v>
+        <v>719.52</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>2171.72</v>
+        <v>2237.57</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>452.44</v>
+        <v>466.16</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>8983.370000000001</v>
+        <v>9255.77</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>5215.67</v>
+        <v>5370.7</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>142.88</v>
+        <v>143.29</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>3013.15</v>
+        <v>3028.72</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>4334.67</v>
+        <v>4373.28</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2240</v>
+        <v>2259.95</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>716.85</v>
+        <v>723.24</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1391.52</v>
+        <v>1390.09</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>5700.83</v>
+        <v>5694.95</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>556.61</v>
+        <v>556.03</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>209.55</v>
+        <v>209.24</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>3943.62</v>
+        <v>3937.82</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>5028.61</v>
+        <v>4998.97</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>604.61</v>
+        <v>602.27</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>4381.13</v>
+        <v>4574.61</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>3239.95</v>
+        <v>3334.06</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>992.05</v>
+        <v>1020.86</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1984.09</v>
+        <v>2016.79</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>138.11</v>
+        <v>140.38</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>3055.48</v>
+        <v>3016.14</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>431.16</v>
+        <v>438.97</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>1647.85</v>
+        <v>1677.73</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1764.91</v>
+        <v>1796.91</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>1254.09</v>
+        <v>1276.83</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1150.9</v>
+        <v>1171.77</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>1346.4</v>
+        <v>1367.49</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>3704.41</v>
+        <v>3762.44</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>2059.2</v>
+        <v>2091.45</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>1719.55</v>
+        <v>1719.46</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>1289.01</v>
+        <v>1288.95</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>6589.41</v>
+        <v>6559.95</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>334.02</v>
+        <v>335.4</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>334.02</v>
+        <v>335.4</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>334.02</v>
+        <v>335.4</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>1035.81</v>
+        <v>1040.09</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>334.02</v>
+        <v>335.4</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>334.02</v>
+        <v>335.4</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>334.02</v>
+        <v>335.4</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>334.02</v>
+        <v>335.4</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>334.02</v>
+        <v>335.4</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>334.02</v>
+        <v>335.4</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>334.02</v>
+        <v>335.4</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>133.21</v>
+        <v>133.76</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>385.42</v>
+        <v>387.01</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>1090.59</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>119.08</v>
+        <v>117.3</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>421.39</v>
+        <v>415.1</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>1098.59</v>
+        <v>1092.28</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>4501.48</v>
+        <v>4472.64</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>3055.45</v>
+        <v>3035.87</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>3695.95</v>
+        <v>3642.48</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>19766.08</v>
+        <v>19340.81</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>45.95</v>
+        <v>44.96</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>5522.17</v>
+        <v>5346.09</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>186.7</v>
+        <v>181.79</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>3341.39</v>
+        <v>3253.4</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>175.74</v>
+        <v>171.11</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>570.95</v>
+        <v>560.6</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>4198.8</v>
+        <v>4122.66</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>459.23</v>
+        <v>463.13</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>181.6</v>
+        <v>181.29</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>2115.59</v>
+        <v>2112.05</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>1268.35</v>
+        <v>1266.22</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>231.09</v>
+        <v>230.7</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>864.78</v>
+        <v>875.42</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>231.09</v>
+        <v>234.16</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>1679.61</v>
+        <v>1701.97</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>9057.74</v>
+        <v>9178.32</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>367.45</v>
+        <v>374.4</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>6658.92</v>
+        <v>6718.91</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>909.71</v>
+        <v>917.9</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>172.96</v>
+        <v>174.51</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>13624.4</v>
+        <v>13711.54</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>3996.05</v>
+        <v>4021.6</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>10268.76</v>
+        <v>10301.07</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>671.15</v>
+        <v>672.54</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>877.9</v>
+        <v>874.13</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>548.6900000000001</v>
+        <v>546.33</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>10376.32</v>
+        <v>10235.25</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>300.98</v>
+        <v>296.88</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>171.41</v>
+        <v>169.95</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>1485.58</v>
+        <v>1502.2</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>999.55</v>
+        <v>1010.73</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>9640.25</v>
+        <v>9676.77</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>149.56</v>
+        <v>150.13</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1870.72</v>
+        <v>1877.81</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>25222.47</v>
+        <v>25318.02</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>2223.11</v>
+        <v>2217.49</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>279.38</v>
+        <v>278.67</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>124.64</v>
+        <v>124.32</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>796.9</v>
+        <v>804.48</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>2152.73</v>
+        <v>2163.3</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>3449.51</v>
+        <v>3466.45</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>6692.25</v>
+        <v>6714.45</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>13815.93</v>
+        <v>13859.9</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>12299.55</v>
+        <v>12338.7</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>567.0599999999999</v>
+        <v>568.87</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>12913.18</v>
+        <v>12981.85</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>3740.44</v>
+        <v>3793.97</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>1364.95</v>
+        <v>1378.83</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>165.58</v>
+        <v>167.13</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>19921.33</v>
+        <v>19647.61</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>397.39</v>
+        <v>394.93</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>490.34</v>
+        <v>492.57</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>1124.95</v>
+        <v>1141.7</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>604.1900000000001</v>
+        <v>617.8099999999999</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>672.24</v>
+        <v>674.3200000000001</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>3321.07</v>
+        <v>3331.34</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>829.6900000000001</v>
+        <v>827.5</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>992.96</v>
+        <v>979.74</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>11065.85</v>
+        <v>10918.45</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>161.82</v>
+        <v>163.36</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>6456.09</v>
+        <v>6481.29</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>3489.95</v>
+        <v>3503.57</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>647.3</v>
+        <v>649.83</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>327.48</v>
+        <v>328.76</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>3263.71</v>
+        <v>3276.45</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>11006.77</v>
+        <v>11116.99</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>10088.88</v>
+        <v>10189.91</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>6312.88</v>
+        <v>6376.1</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>3395.11</v>
+        <v>3429.11</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>1417.31</v>
+        <v>1422.83</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>10522.47</v>
+        <v>10546.6</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>761.1900000000001</v>
+        <v>766.28</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>1028.23</v>
+        <v>1024.98</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>1268.65</v>
+        <v>1265.89</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>1332.56</v>
+        <v>1329.89</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>8739.23</v>
+        <v>8599.110000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/gas-licuado-de-petroleo/antofagasta.xlsx
+++ b/docs/oc-regiones/gas-licuado-de-petroleo/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M178"/>
+  <dimension ref="A1:M183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>707415-154-CM25</t>
+          <t>1079454-458-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1147.41</v>
+        <v>1338.42</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3048-38-CM25</t>
+          <t>1171326-45-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.102.092-9</t>
+          <t>61.926.300-6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Centro Telecomunicaciones Navales de Antofagasta</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>106.28</v>
+        <v>143.98</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1171326-63-CM25</t>
+          <t>2258-22401-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.926.300-6</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile CET Antofagasta II Región</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>63.58</v>
+        <v>12429.34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>778989-187-CM25</t>
+          <t>778992-323-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>65.081.190-9</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3a Briagada Acorazada "La Concepción"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1141.11</v>
+        <v>329.08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1346284-200-CM25</t>
+          <t>2258-25863-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>3172.26</v>
+        <v>5350.91</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2258-25919-CM25</t>
+          <t>707415-154-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,22 +834,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>9351.16</v>
+        <v>1147.41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2258-25921-CM25</t>
+          <t>1171326-63-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.926.300-6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>Gendarmería de Chile CET Antofagasta II Región</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>5430.19</v>
+        <v>63.58</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2258-25923-CM25</t>
+          <t>3048-38-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.102.092-9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>Centro Telecomunicaciones Navales de Antofagasta</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>3743.58</v>
+        <v>106.28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2258-25924-CM25</t>
+          <t>778989-187-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>65.081.190-9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>3a Briagada Acorazada "La Concepción"</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>6889.41</v>
+        <v>1141.11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2258-26373-CM25</t>
+          <t>1346284-200-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>884.78</v>
+        <v>3172.26</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2258-26371-CM25</t>
+          <t>2258-25919-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>7837.57</v>
+        <v>9351.16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2258-26175-CM25</t>
+          <t>2258-25921-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>464.19</v>
+        <v>5430.19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2258-26227-CM25</t>
+          <t>2258-25923-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>7001.32</v>
+        <v>3743.58</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1410-1147-CM25</t>
+          <t>2258-25924-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1024.6</v>
+        <v>6889.41</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2258-26699-CM25</t>
+          <t>2258-26371-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>6407.27</v>
+        <v>7837.57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2258-26880-CM25</t>
+          <t>2258-26227-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>6235.65</v>
+        <v>7001.32</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1410-1162-CM25</t>
+          <t>2258-26373-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>3125.79</v>
+        <v>884.78</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3174-254-CM25</t>
+          <t>2258-26175-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.102.045-7</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE ANTOFAGASTA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>547.03</v>
+        <v>464.19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1573-181-CM25</t>
+          <t>1410-1147-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2294.63</v>
+        <v>1024.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1171326-68-CM25</t>
+          <t>2258-26699-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.926.300-6</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile CET Antofagasta II Región</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>140.01</v>
+        <v>6407.27</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1080164-37-CM25</t>
+          <t>2258-26880-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ESCUELA DE SUBOFICIALES GRUPO ANTOFAGASTA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>487.89</v>
+        <v>6235.65</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2258-27136-CM25</t>
+          <t>1410-1162-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>6333.88</v>
+        <v>3125.79</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1123-71-CM25</t>
+          <t>3174-254-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>61.102.045-7</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>GOBERNACION MARITIMA DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>426.72</v>
+        <v>547.03</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>838098-91-CM25</t>
+          <t>1573-181-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Antofagasta" Bienestar Social</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>291.75</v>
+        <v>2294.63</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>778992-358-CM25</t>
+          <t>1171326-68-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,22 +1993,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>61.926.300-6</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>Gendarmería de Chile CET Antofagasta II Región</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>141.33</v>
+        <v>140.01</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1775-69-CM25</t>
+          <t>1080164-37-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>60.804.004-8</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE ANTOFAGASTA</t>
+          <t>ESCUELA DE SUBOFICIALES GRUPO ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>435.02</v>
+        <v>487.89</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2430-404-CM25</t>
+          <t>1123-71-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>19489.71</v>
+        <v>426.72</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2258-27531-CM25</t>
+          <t>2258-27136-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>3946.14</v>
+        <v>6333.88</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2258-27527-CM25</t>
+          <t>838098-91-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>Zona Bienestar "Antofagasta" Bienestar Social</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2236.76</v>
+        <v>291.75</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1410-1230-CM25</t>
+          <t>778992-358-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>Regimiento Reforzado N° 1 "Calama"</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>421.33</v>
+        <v>141.33</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1410-1241-CM25</t>
+          <t>1775-69-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>60.804.004-8</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>DIRECCIÓN REGIONAL ADUANA DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>368.47</v>
+        <v>435.02</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1079454-712-CM25</t>
+          <t>2430-404-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,22 +2420,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>551.67</v>
+        <v>19489.71</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>778992-368-CM25</t>
+          <t>2258-27527-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1339.1</v>
+        <v>2236.76</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2258-28508-CM25</t>
+          <t>2258-27531-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>6055.12</v>
+        <v>3946.14</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>796305-86-CM25</t>
+          <t>1410-1230-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,22 +2603,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>18101.87</v>
+        <v>421.33</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1410-2647-CM25</t>
+          <t>1410-1241-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1424.42</v>
+        <v>368.47</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1171326-72-CM25</t>
+          <t>1079454-712-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,22 +2725,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.926.300-6</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile CET Antofagasta II Región</t>
+          <t>SECCIÓN COMPRAS II ZONA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>138.06</v>
+        <v>551.67</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2258-28663-CM25</t>
+          <t>778992-368-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>Regimiento Reforzado N° 1 "Calama"</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>6054.07</v>
+        <v>1339.1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2258-260-CM26</t>
+          <t>2258-28508-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>5431.36</v>
+        <v>6055.12</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2258-258-CM26</t>
+          <t>796305-86-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>Division de Bienestar Social</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>4790.51</v>
+        <v>18101.87</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3506-51-CM26</t>
+          <t>1410-2647-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2964,27 +2964,27 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>47968.67</v>
+        <v>1424.42</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2258-582-CM26</t>
+          <t>1171326-72-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.926.300-6</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>Gendarmería de Chile CET Antofagasta II Región</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>4883.46</v>
+        <v>138.06</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2258-581-CM26</t>
+          <t>2258-28663-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>6522.81</v>
+        <v>6054.07</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1410-30-CM26</t>
+          <t>2258-258-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,22 +3152,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>962.16</v>
+        <v>4790.51</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2258-700-CM26</t>
+          <t>2258-260-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,12 +3213,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>470.15</v>
+        <v>5431.36</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1410-36-CM26</t>
+          <t>3506-51-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,22 +3274,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>4876.08</v>
+        <v>47968.67</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1173417-2-CM26</t>
+          <t>2258-581-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3335,22 +3335,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>65.070.600-5</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Ojo de Opache</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>719.52</v>
+        <v>6522.81</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>707415-6-CM26</t>
+          <t>2258-582-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3396,22 +3396,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>2237.57</v>
+        <v>4883.46</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>707415-7-CM26</t>
+          <t>1410-30-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>466.16</v>
+        <v>962.16</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2385-50-CM26</t>
+          <t>2258-700-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3518,22 +3518,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>9255.77</v>
+        <v>470.15</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2258-739-CM26</t>
+          <t>1410-36-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>5370.7</v>
+        <v>4876.08</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1171326-1-CM26</t>
+          <t>1173417-2-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3635,27 +3635,27 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.926.300-6</t>
+          <t>65.070.600-5</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile CET Antofagasta II Región</t>
+          <t>Centro de Educación y Trabajo Ojo de Opache</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>143.29</v>
+        <v>719.52</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1410-83-CM26</t>
+          <t>707415-6-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3696,27 +3696,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>3028.72</v>
+        <v>2237.57</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2258-1269-CM26</t>
+          <t>707415-7-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3757,27 +3757,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>4373.28</v>
+        <v>466.16</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2258-1270-CM26</t>
+          <t>2385-50-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2259.95</v>
+        <v>9255.77</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>778992-2-CM26</t>
+          <t>2258-739-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>723.24</v>
+        <v>5370.7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1410-102-CM26</t>
+          <t>1171326-1-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.926.300-6</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>Gendarmería de Chile CET Antofagasta II Región</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1390.09</v>
+        <v>143.29</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2258-1423-CM26</t>
+          <t>1410-83-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>5694.95</v>
+        <v>3028.72</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3174-20-CM26</t>
+          <t>2258-1269-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.102.045-7</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE ANTOFAGASTA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>556.03</v>
+        <v>4373.28</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2122-18-CM26</t>
+          <t>2258-1270-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>209.24</v>
+        <v>2259.95</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2258-1470-CM26</t>
+          <t>778992-2-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>Regimiento Reforzado N° 1 "Calama"</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>3937.82</v>
+        <v>723.24</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2258-1606-CM26</t>
+          <t>1410-102-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>4998.97</v>
+        <v>1390.09</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>778992-22-CM26</t>
+          <t>2258-1423-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>602.27</v>
+        <v>5694.95</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2258-1802-CM26</t>
+          <t>3174-20-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.102.045-7</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>GOBERNACION MARITIMA DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>4574.61</v>
+        <v>556.03</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1230848-21-CM26</t>
+          <t>2122-18-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4428,27 +4428,27 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>70.954.900-6</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>CCorporación Municipal de Desarrollo Social de Cal</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>3334.06</v>
+        <v>209.24</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1057385-55-CM26</t>
+          <t>2258-1470-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4489,12 +4489,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1020.86</v>
+        <v>3937.82</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1410-152-CM26</t>
+          <t>2258-1606-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>2016.79</v>
+        <v>4998.97</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1171326-11-CM26</t>
+          <t>778992-22-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.926.300-6</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile CET Antofagasta II Región</t>
+          <t>Regimiento Reforzado N° 1 "Calama"</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>140.38</v>
+        <v>602.27</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1795-16-CM26</t>
+          <t>2258-1802-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4677,22 +4677,22 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>60.908.000-0</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>3016.14</v>
+        <v>4574.61</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3274-67-CM26</t>
+          <t>1230848-21-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4738,22 +4738,22 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>70.954.900-6</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>CCorporación Municipal de Desarrollo Social de Cal</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>438.97</v>
+        <v>3334.06</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>769-142-CM26</t>
+          <t>1057385-55-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>1677.73</v>
+        <v>1020.86</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>3274-66-CM26</t>
+          <t>1410-152-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1796.91</v>
+        <v>2016.79</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1079454-57-CM26</t>
+          <t>1171326-11-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>61.926.300-6</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>Gendarmería de Chile CET Antofagasta II Región</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>1276.83</v>
+        <v>140.38</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>778992-46-CM26</t>
+          <t>1795-16-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4982,22 +4982,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>60.908.000-0</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1171.77</v>
+        <v>3016.14</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2258-2009-CM26</t>
+          <t>1079454-57-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SECCIÓN COMPRAS II ZONA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>1367.49</v>
+        <v>1276.83</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2258-2013-CM26</t>
+          <t>778992-46-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>Regimiento Reforzado N° 1 "Calama"</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>3762.44</v>
+        <v>1171.77</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>778989-33-CM26</t>
+          <t>769-142-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>65.081.190-9</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>3a Briagada Acorazada "La Concepción"</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>2091.45</v>
+        <v>1677.73</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1013609-26-CM26</t>
+          <t>3274-66-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>65.158.175-3</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. Campo Militar "Antofagasta"</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>1719.46</v>
+        <v>1796.91</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>778992-47-CM26</t>
+          <t>3274-67-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>1288.95</v>
+        <v>438.97</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2258-2215-CM26</t>
+          <t>778989-33-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>65.081.190-9</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>3a Briagada Acorazada "La Concepción"</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>6559.95</v>
+        <v>2091.45</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1233623-60-CM26</t>
+          <t>2258-2009-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5419,12 +5419,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>335.4</v>
+        <v>1367.49</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1233623-61-CM26</t>
+          <t>2258-2013-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>335.4</v>
+        <v>3762.44</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1233623-58-CM26</t>
+          <t>1013609-26-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>65.158.175-3</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>Jefatura Adm. y Log. Campo Militar "Antofagasta"</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>335.4</v>
+        <v>1719.46</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1410-205-CM26</t>
+          <t>778992-47-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>Regimiento Reforzado N° 1 "Calama"</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>1040.09</v>
+        <v>1288.95</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1233623-62-CM26</t>
+          <t>2258-2215-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>335.4</v>
+        <v>6559.95</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1233623-57-CM26</t>
+          <t>1233623-59-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5760,7 +5760,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1233623-59-CM26</t>
+          <t>1410-205-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>335.4</v>
+        <v>1040.09</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1233623-55-CM26</t>
+          <t>1233623-62-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5882,7 +5882,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1233623-56-CM26</t>
+          <t>1233623-61-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5943,7 +5943,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1233623-54-CM26</t>
+          <t>1233623-60-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6004,7 +6004,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1233623-53-CM26</t>
+          <t>1233623-58-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6065,7 +6065,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1233623-52-CM26</t>
+          <t>1233623-56-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6105,12 +6105,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>133.76</v>
+        <v>335.4</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1233623-51-CM26</t>
+          <t>1233623-57-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>387.01</v>
+        <v>335.4</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>778992-51-CM26</t>
+          <t>1233623-55-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6212,12 +6212,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>1078</v>
+        <v>335.4</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>3048-8-CM26</t>
+          <t>1233623-54-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.102.092-9</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Centro Telecomunicaciones Navales de Antofagasta</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>117.3</v>
+        <v>335.4</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>3048-9-CM26</t>
+          <t>1233623-53-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.102.092-9</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Centro Telecomunicaciones Navales de Antofagasta</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>415.1</v>
+        <v>335.4</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>778998-39-CM26</t>
+          <t>1233623-52-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.964.800-5</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Regimiento Logístico N° 1 "Tocopilla"</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>1092.28</v>
+        <v>133.76</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2258-2465-CM26</t>
+          <t>1233623-51-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>4472.64</v>
+        <v>387.01</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1410-237-CM26</t>
+          <t>778992-51-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6517,12 +6517,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>Regimiento Reforzado N° 1 "Calama"</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>3035.87</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>778992-66-CM26</t>
+          <t>3048-8-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>61.102.092-9</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>Centro Telecomunicaciones Navales de Antofagasta</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>3642.48</v>
+        <v>117.3</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2430-68-CM26</t>
+          <t>3048-9-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>61.102.092-9</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>Centro Telecomunicaciones Navales de Antofagasta</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6669,13 +6669,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>19340.81</v>
+        <v>415.1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1171326-13-CM26</t>
+          <t>778998-39-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.926.300-6</t>
+          <t>61.964.800-5</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile CET Antofagasta II Región</t>
+          <t>Regimiento Logístico N° 1 "Tocopilla"</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6730,13 +6730,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>44.96</v>
+        <v>1092.28</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2258-2540-CM26</t>
+          <t>2258-2465-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6746,12 +6746,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>5346.09</v>
+        <v>4472.64</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1997-13-CM26</t>
+          <t>1410-237-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6807,27 +6807,27 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>60.511.023-1</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE EL LOA</t>
+          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6852,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>181.79</v>
+        <v>3035.87</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1346284-77-CM26</t>
+          <t>778992-66-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6868,12 +6868,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>Regimiento Reforzado N° 1 "Calama"</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>3253.4</v>
+        <v>3642.48</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1171326-16-CM26</t>
+          <t>2430-68-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>61.926.300-6</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile CET Antofagasta II Región</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>171.11</v>
+        <v>19340.81</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1080164-13-CM26</t>
+          <t>1171326-13-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6990,12 +6990,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>61.926.300-6</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>ESCUELA DE SUBOFICIALES GRUPO ANTOFAGASTA</t>
+          <t>Gendarmería de Chile CET Antofagasta II Región</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7020,12 +7020,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>560.6</v>
+        <v>44.96</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2258-2845-CM26</t>
+          <t>2258-2540-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7096,13 +7096,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>4122.66</v>
+        <v>5346.09</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1080164-16-CM26</t>
+          <t>1997-13-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7117,22 +7117,22 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>60.511.023-1</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>ESCUELA DE SUBOFICIALES GRUPO ANTOFAGASTA</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE EL LOA</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7142,12 +7142,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7157,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>463.13</v>
+        <v>181.79</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>778992-73-CM26</t>
+          <t>1346284-77-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7218,13 +7218,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>181.29</v>
+        <v>3253.4</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1158-45-CM26</t>
+          <t>1171326-16-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7239,22 +7239,22 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.926.300-6</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>Gendarmería de Chile CET Antofagasta II Región</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -7279,13 +7279,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>2112.05</v>
+        <v>171.11</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1410-304-CM26</t>
+          <t>1080164-13-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>ESCUELA DE SUBOFICIALES GRUPO ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7340,13 +7340,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>1266.22</v>
+        <v>560.6</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1997-15-CM26</t>
+          <t>2258-2845-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7361,22 +7361,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>60.511.023-1</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE EL LOA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7401,13 +7401,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>230.7</v>
+        <v>4122.66</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1233623-149-CM26</t>
+          <t>1080164-16-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7432,12 +7432,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>ESCUELA DE SUBOFICIALES GRUPO ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7462,13 +7462,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>875.42</v>
+        <v>463.13</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>778989-65-CM26</t>
+          <t>778992-73-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>65.081.190-9</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>3a Briagada Acorazada "La Concepción"</t>
+          <t>Regimiento Reforzado N° 1 "Calama"</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7523,13 +7523,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>234.16</v>
+        <v>181.29</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2258-3139-CM26</t>
+          <t>1158-45-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7544,22 +7544,22 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7584,13 +7584,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>1701.97</v>
+        <v>2112.05</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2258-3140-CM26</t>
+          <t>1410-304-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -7645,13 +7645,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>9178.32</v>
+        <v>1266.22</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1410-312-CM26</t>
+          <t>1997-15-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7666,22 +7666,22 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>60.511.023-1</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE EL LOA</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7706,13 +7706,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>374.4</v>
+        <v>230.7</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2258-3327-CM26</t>
+          <t>1233623-149-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -7767,13 +7767,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>6718.91</v>
+        <v>875.42</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1233623-165-CM26</t>
+          <t>778989-65-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7798,12 +7798,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>65.081.190-9</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>3a Briagada Acorazada "La Concepción"</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7813,12 +7813,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -7828,13 +7828,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>917.9</v>
+        <v>234.16</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>778992-77-CM26</t>
+          <t>2258-3139-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7874,12 +7874,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -7889,13 +7889,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>174.51</v>
+        <v>1701.97</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1079454-122-CM26</t>
+          <t>2258-3140-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7910,22 +7910,22 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7950,13 +7950,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>13711.54</v>
+        <v>9178.32</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>707415-54-CM26</t>
+          <t>1410-312-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7971,22 +7971,22 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8011,13 +8011,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>4021.6</v>
+        <v>374.4</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2258-3417-CM26</t>
+          <t>2258-3327-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8072,13 +8072,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>10301.07</v>
+        <v>6718.91</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>3174-77-CM26</t>
+          <t>1233623-165-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.102.045-7</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE ANTOFAGASTA</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>672.54</v>
+        <v>917.9</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1113265-36-CM26</t>
+          <t>778992-77-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>62.000.770-6</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ANTOFAGASTA</t>
+          <t>Regimiento Reforzado N° 1 "Calama"</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -8194,13 +8194,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>874.13</v>
+        <v>174.51</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2258-3593-CM26</t>
+          <t>1079454-122-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8215,22 +8215,22 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SECCIÓN COMPRAS II ZONA</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8240,12 +8240,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -8255,13 +8255,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>546.33</v>
+        <v>13711.54</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2258-3690-CM26</t>
+          <t>707415-54-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8271,27 +8271,27 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8316,13 +8316,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>10235.25</v>
+        <v>4021.6</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1997-22-CM26</t>
+          <t>2258-3417-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8332,27 +8332,27 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>60.511.023-1</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE EL LOA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8377,13 +8377,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>296.88</v>
+        <v>10301.07</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1171326-21-CM26</t>
+          <t>3174-77-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>61.926.300-6</t>
+          <t>61.102.045-7</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile CET Antofagasta II Región</t>
+          <t>GOBERNACION MARITIMA DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8438,13 +8438,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>169.95</v>
+        <v>672.54</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>778992-119-CM26</t>
+          <t>1113265-36-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8454,27 +8454,27 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>62.000.770-6</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -8499,13 +8499,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>1502.2</v>
+        <v>874.13</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1079454-143-CM26</t>
+          <t>2258-3593-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8515,27 +8515,27 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -8560,13 +8560,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>1010.73</v>
+        <v>546.33</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2258-3883-CM26</t>
+          <t>2258-3690-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8621,13 +8621,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>9676.77</v>
+        <v>10235.25</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1171326-27-CM26</t>
+          <t>1997-22-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8642,22 +8642,22 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>61.926.300-6</t>
+          <t>60.511.023-1</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile CET Antofagasta II Región</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE EL LOA</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8682,13 +8682,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>150.13</v>
+        <v>296.88</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2385-328-CM26</t>
+          <t>1171326-21-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8703,22 +8703,22 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>61.926.300-6</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>Gendarmería de Chile CET Antofagasta II Región</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8728,12 +8728,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
@@ -8743,13 +8743,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1877.81</v>
+        <v>169.95</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2385-329-CM26</t>
+          <t>778992-119-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>Regimiento Reforzado N° 1 "Calama"</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>25318.02</v>
+        <v>1502.2</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1013609-60-CM26</t>
+          <t>1079454-143-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8825,22 +8825,22 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>65.158.175-3</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. Campo Militar "Antofagasta"</t>
+          <t>SECCIÓN COMPRAS II ZONA</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8865,13 +8865,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>2217.49</v>
+        <v>1010.73</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1233623-191-CM26</t>
+          <t>2258-3883-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8886,7 +8886,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -8926,13 +8926,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>278.67</v>
+        <v>9676.77</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1233623-192-CM26</t>
+          <t>1171326-27-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.926.300-6</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>Gendarmería de Chile CET Antofagasta II Región</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8987,13 +8987,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>124.32</v>
+        <v>150.13</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1573-15-CM26</t>
+          <t>2385-328-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9008,22 +9008,22 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9048,13 +9048,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>804.48</v>
+        <v>1877.81</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>3053-14-CM26</t>
+          <t>2385-329-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9069,22 +9069,22 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>69.252.500-0</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9109,13 +9109,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>2163.3</v>
+        <v>25318.02</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1410-428-CM26</t>
+          <t>1013609-60-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9130,7 +9130,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9140,12 +9140,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>65.158.175-3</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>Jefatura Adm. y Log. Campo Militar "Antofagasta"</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9170,13 +9170,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>3466.45</v>
+        <v>2217.49</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1410-435-CM26</t>
+          <t>1233623-191-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -9231,13 +9231,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>6714.45</v>
+        <v>278.67</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2258-4569-CM26</t>
+          <t>1233623-192-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9252,7 +9252,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -9262,12 +9262,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9292,13 +9292,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>13859.9</v>
+        <v>124.32</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2258-4570-CM26</t>
+          <t>1573-15-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -9323,12 +9323,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9353,13 +9353,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>12338.7</v>
+        <v>804.48</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1775-33-CM26</t>
+          <t>1410-428-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9384,12 +9384,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>60.804.004-8</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE ANTOFAGASTA</t>
+          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9414,13 +9414,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>568.87</v>
+        <v>3466.45</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2258-4659-CM26</t>
+          <t>3053-14-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>69.252.500-0</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9475,13 +9475,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>12981.85</v>
+        <v>2163.3</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>778992-157-CM26</t>
+          <t>1410-435-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9491,12 +9491,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9536,13 +9536,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>3793.97</v>
+        <v>6714.45</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1410-405-CM26</t>
+          <t>2258-4569-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -9567,12 +9567,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9582,12 +9582,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -9597,13 +9597,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>1378.83</v>
+        <v>13859.9</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1171326-32-CM26</t>
+          <t>2258-4570-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9613,12 +9613,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>61.926.300-6</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile CET Antofagasta II Región</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9643,12 +9643,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -9658,13 +9658,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>167.13</v>
+        <v>12338.7</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2430-167-CM26</t>
+          <t>1775-33-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9674,27 +9674,27 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>60.804.004-8</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>DIRECCIÓN REGIONAL ADUANA DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9719,13 +9719,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>19647.61</v>
+        <v>568.87</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1410-519-CM26</t>
+          <t>2258-4659-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -9750,12 +9750,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -9780,13 +9780,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>394.93</v>
+        <v>12981.85</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>778992-166-CM26</t>
+          <t>778992-157-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9841,13 +9841,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>492.57</v>
+        <v>3793.97</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1057384-495-CM26</t>
+          <t>1410-405-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9862,7 +9862,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9872,12 +9872,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9902,13 +9902,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>1141.7</v>
+        <v>1378.83</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1123-22-CM26</t>
+          <t>1171326-32-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>61.926.300-6</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>Gendarmería de Chile CET Antofagasta II Región</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
@@ -9963,13 +9963,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>617.8099999999999</v>
+        <v>167.13</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>838098-29-CM26</t>
+          <t>2430-167-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9984,22 +9984,22 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Antofagasta" Bienestar Social</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10024,13 +10024,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>674.3200000000001</v>
+        <v>19647.61</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1346284-108-CM26</t>
+          <t>1410-519-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10045,7 +10045,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -10055,12 +10055,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10070,12 +10070,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -10085,13 +10085,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>3331.34</v>
+        <v>394.93</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>778998-102-CM26</t>
+          <t>778992-166-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10106,7 +10106,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -10116,12 +10116,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>61.964.800-5</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Regimiento Logístico N° 1 "Tocopilla"</t>
+          <t>Regimiento Reforzado N° 1 "Calama"</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10131,12 +10131,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -10146,13 +10146,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>827.5</v>
+        <v>492.57</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>778992-167-CM26</t>
+          <t>1057384-495-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -10177,12 +10177,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -10207,13 +10207,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>979.74</v>
+        <v>1141.7</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>796305-30-CM26</t>
+          <t>1123-22-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -10238,12 +10238,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10268,13 +10268,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>10918.45</v>
+        <v>617.8099999999999</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1171326-38-CM26</t>
+          <t>838098-29-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10284,27 +10284,27 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>61.926.300-6</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile CET Antofagasta II Región</t>
+          <t>Zona Bienestar "Antofagasta" Bienestar Social</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
@@ -10329,13 +10329,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>163.36</v>
+        <v>674.3200000000001</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2258-5544-CM26</t>
+          <t>1346284-108-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10345,12 +10345,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -10390,13 +10390,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>6481.29</v>
+        <v>3331.34</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2258-5542-CM26</t>
+          <t>778998-102-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -10421,12 +10421,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.964.800-5</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>Regimiento Logístico N° 1 "Tocopilla"</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K164" t="inlineStr"/>
@@ -10451,13 +10451,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>3503.57</v>
+        <v>827.5</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>3174-127-CM26</t>
+          <t>778992-167-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10467,12 +10467,12 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -10482,12 +10482,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>61.102.045-7</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE ANTOFAGASTA</t>
+          <t>Regimiento Reforzado N° 1 "Calama"</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10497,12 +10497,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
@@ -10512,13 +10512,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>649.83</v>
+        <v>979.74</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>778992-175-CM26</t>
+          <t>796305-30-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10528,12 +10528,12 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -10543,12 +10543,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>Division de Bienestar Social</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10558,12 +10558,12 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
@@ -10573,13 +10573,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>328.76</v>
+        <v>10918.45</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1410-571-CM26</t>
+          <t>1171326-38-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10594,22 +10594,22 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.926.300-6</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>Gendarmería de Chile CET Antofagasta II Región</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
@@ -10634,13 +10634,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>3276.45</v>
+        <v>163.36</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2258-5571-CM26</t>
+          <t>2258-5544-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10655,7 +10655,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10695,13 +10695,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>11116.99</v>
+        <v>6481.29</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2258-5573-CM26</t>
+          <t>2258-5542-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -10756,13 +10756,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>10189.91</v>
+        <v>3503.57</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2258-5616-CM26</t>
+          <t>3174-127-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.102.045-7</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>GOBERNACION MARITIMA DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10802,12 +10802,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K170" t="inlineStr"/>
@@ -10817,13 +10817,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>6376.1</v>
+        <v>649.83</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2258-5617-CM26</t>
+          <t>778992-175-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10848,12 +10848,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>Regimiento Reforzado N° 1 "Calama"</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10863,12 +10863,12 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K171" t="inlineStr"/>
@@ -10878,13 +10878,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>3429.11</v>
+        <v>328.76</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>778992-196-CM26</t>
+          <t>1410-571-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K172" t="inlineStr"/>
@@ -10939,13 +10939,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>1422.83</v>
+        <v>3276.45</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2258-5569-CM26</t>
+          <t>2258-5571-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10960,7 +10960,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -11000,13 +11000,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>10546.6</v>
+        <v>11116.99</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>838098-33-CM26</t>
+          <t>2258-5573-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11021,22 +11021,22 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Antofagasta" Bienestar Social</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11046,12 +11046,12 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K174" t="inlineStr"/>
@@ -11061,13 +11061,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>766.28</v>
+        <v>10189.91</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1173417-13-CM26</t>
+          <t>2258-5616-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11082,22 +11082,22 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>65.070.600-5</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Ojo de Opache</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11122,13 +11122,13 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>1024.98</v>
+        <v>6376.1</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1410-643-CM26</t>
+          <t>2258-5617-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11143,7 +11143,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K176" t="inlineStr"/>
@@ -11183,13 +11183,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>1265.89</v>
+        <v>3429.11</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1410-562-CM26</t>
+          <t>778992-196-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11204,22 +11204,22 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>Regimiento Reforzado N° 1 "Calama"</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11244,13 +11244,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>1329.89</v>
+        <v>1422.83</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2258-6179-CM26</t>
+          <t>2258-5569-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11265,7 +11265,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -11305,6 +11305,311 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
+        <v>10546.6</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>838098-33-CM26</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>73.923.800-5</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Zona Bienestar "Antofagasta" Bienestar Social</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="n">
+        <v>766.28</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>1173417-13-CM26</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>65.070.600-5</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Centro de Educación y Trabajo Ojo de Opache</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M180" s="2" t="n">
+        <v>1024.98</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>1410-643-CM26</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>61.004.007-1</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="n">
+        <v>1265.89</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>1410-562-CM26</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>61.004.007-1</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M182" s="2" t="n">
+        <v>1329.89</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2258-6179-CM26</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>61.606.201-8</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="n">
         <v>8599.110000000001</v>
       </c>
     </row>

--- a/docs/oc-regiones/gas-licuado-de-petroleo/antofagasta.xlsx
+++ b/docs/oc-regiones/gas-licuado-de-petroleo/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M468"/>
+  <dimension ref="A1:M486"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -904,7 +904,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3174-6-CM25</t>
+          <t>2258-5111-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -924,17 +924,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.102.045-7</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1993.4</v>
+        <v>10656.35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2258-5107-CM25</t>
+          <t>2258-5110-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1028,13 +1028,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>7805.79</v>
+        <v>9832.92</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2258-5110-CM25</t>
+          <t>3174-6-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1054,17 +1054,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.102.045-7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1093,13 +1093,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>9832.92</v>
+        <v>1993.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2258-5111-CM25</t>
+          <t>2258-5107-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1158,13 +1158,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>10656.35</v>
+        <v>7805.79</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1423498-2-CM25</t>
+          <t>1410-87-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1204,17 +1204,17 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1223,13 +1223,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>84.73</v>
+        <v>5088.36</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1410-87-CM25</t>
+          <t>1423498-2-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1269,17 +1269,17 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>5088.36</v>
+        <v>84.73</v>
       </c>
     </row>
     <row r="14">
@@ -1749,7 +1749,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1410-184-CM25</t>
+          <t>2258-9293-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1808,7 +1808,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>245.24</v>
+        <v>6494.21</v>
       </c>
     </row>
     <row r="22">
@@ -1879,7 +1879,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2258-9293-CM25</t>
+          <t>1410-184-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1938,13 +1938,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>6494.21</v>
+        <v>245.24</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2258-9306-CM25</t>
+          <t>2258-9307-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2003,13 +2003,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>6310.31</v>
+        <v>841.16</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2258-9307-CM25</t>
+          <t>2258-9306-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2068,13 +2068,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>841.16</v>
+        <v>6310.31</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2258-9355-CM25</t>
+          <t>922070-20-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>65.117.365-5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2133,13 +2133,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>9147.469999999999</v>
+        <v>726.8099999999999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2258-9358-CM25</t>
+          <t>2258-9365-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>6894.17</v>
+        <v>7915.81</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2258-9360-CM25</t>
+          <t>2258-9362-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2263,13 +2263,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2280.95</v>
+        <v>7673.32</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>922070-20-CM25</t>
+          <t>2258-9360-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>65.117.365-5</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2328,13 +2328,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>726.8099999999999</v>
+        <v>2280.95</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2258-9362-CM25</t>
+          <t>2258-9358-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2393,13 +2393,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>7673.32</v>
+        <v>6894.17</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2258-9365-CM25</t>
+          <t>2258-9355-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2458,7 +2458,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>7915.81</v>
+        <v>9147.469999999999</v>
       </c>
     </row>
     <row r="32">
@@ -3309,7 +3309,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1158-14-CM25</t>
+          <t>3834-44-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3329,17 +3329,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1253.28</v>
+        <v>79.06999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3834-44-CM25</t>
+          <t>1158-14-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3394,17 +3394,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>79.06999999999999</v>
+        <v>1253.28</v>
       </c>
     </row>
     <row r="47">
@@ -3764,7 +3764,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1171326-3-CM25</t>
+          <t>4051-67-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3789,12 +3789,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.926.300-6</t>
+          <t>69.252.600-7</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3804,17 +3804,17 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3823,13 +3823,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>121.55</v>
+        <v>343.7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4051-67-CM25</t>
+          <t>1171326-3-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>61.926.300-6</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3869,17 +3869,17 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3888,7 +3888,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>343.7</v>
+        <v>121.55</v>
       </c>
     </row>
     <row r="54">
@@ -3959,7 +3959,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1233623-64-CM25</t>
+          <t>1233623-66-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4024,7 +4024,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1233623-61-CM25</t>
+          <t>1233623-65-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4089,7 +4089,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1233623-72-CM25</t>
+          <t>1233623-64-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4148,13 +4148,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>159.74</v>
+        <v>246.73</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1233623-71-CM25</t>
+          <t>1233623-62-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4213,13 +4213,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>3145.86</v>
+        <v>370.1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1233623-67-CM25</t>
+          <t>1233623-61-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4284,7 +4284,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1233623-66-CM25</t>
+          <t>1233623-60-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4343,13 +4343,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>246.73</v>
+        <v>370.1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1233623-70-CM25</t>
+          <t>1233623-67-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>246.73</v>
+        <v>370.1</v>
       </c>
     </row>
     <row r="62">
@@ -4479,7 +4479,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1233623-60-CM25</t>
+          <t>1233623-70-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4538,13 +4538,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>370.1</v>
+        <v>246.73</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1233623-62-CM25</t>
+          <t>1233623-72-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>370.1</v>
+        <v>159.74</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1233623-65-CM25</t>
+          <t>1233623-71-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4668,7 +4668,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>370.1</v>
+        <v>3145.86</v>
       </c>
     </row>
     <row r="66">
@@ -5324,7 +5324,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>993-75-CM25</t>
+          <t>1423498-17-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5344,17 +5344,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5364,17 +5364,17 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5383,13 +5383,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>698.0599999999999</v>
+        <v>92.41</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1423498-17-CM25</t>
+          <t>993-75-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5409,17 +5409,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5429,17 +5429,17 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5448,7 +5448,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>92.41</v>
+        <v>698.0599999999999</v>
       </c>
     </row>
     <row r="78">
@@ -5584,7 +5584,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2258-16251-CM25</t>
+          <t>2258-16274-CM25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5643,13 +5643,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>802.36</v>
+        <v>7969.57</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1057385-125-CM25</t>
+          <t>2258-16258-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5708,13 +5708,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>303.03</v>
+        <v>4387.2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2258-16274-CM25</t>
+          <t>2258-16268-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5773,13 +5773,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>7969.57</v>
+        <v>6869.36</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2258-16268-CM25</t>
+          <t>2258-16251-CM25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5838,13 +5838,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>6869.36</v>
+        <v>802.36</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2385-212-CM25</t>
+          <t>2258-16253-CM25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5903,13 +5903,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>1739.12</v>
+        <v>5569.09</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2258-16253-CM25</t>
+          <t>2258-16249-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5968,13 +5968,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>5569.09</v>
+        <v>444.29</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2258-16249-CM25</t>
+          <t>2258-16244-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6033,13 +6033,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>444.29</v>
+        <v>6355.77</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2258-16244-CM25</t>
+          <t>1057385-125-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6064,12 +6064,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6098,13 +6098,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>6355.77</v>
+        <v>303.03</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2258-16258-CM25</t>
+          <t>2385-212-CM25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>4387.2</v>
+        <v>1739.12</v>
       </c>
     </row>
     <row r="89">
@@ -6299,7 +6299,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1013609-36-CM25</t>
+          <t>1171326-12-CM25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>65.158.175-3</t>
+          <t>61.926.300-6</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6339,17 +6339,17 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>246.21</v>
+        <v>117.48</v>
       </c>
     </row>
     <row r="92">
@@ -6429,7 +6429,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1171326-12-CM25</t>
+          <t>1013609-36-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.926.300-6</t>
+          <t>65.158.175-3</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6469,17 +6469,17 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6488,7 +6488,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>117.48</v>
+        <v>246.21</v>
       </c>
     </row>
     <row r="94">
@@ -7339,7 +7339,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2258-17746-CM25</t>
+          <t>2258-17749-CM25</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7398,13 +7398,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>3465.88</v>
+        <v>7816.33</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2258-17749-CM25</t>
+          <t>2258-17746-CM25</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>7816.33</v>
+        <v>3465.88</v>
       </c>
     </row>
     <row r="109">
@@ -7534,7 +7534,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>3858-196-CM25</t>
+          <t>1997-40-CM25</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7554,17 +7554,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>60.511.023-1</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE EL LOA</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7593,13 +7593,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>115.51</v>
+        <v>133.23</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1997-40-CM25</t>
+          <t>3858-196-CM25</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7619,17 +7619,17 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>60.511.023-1</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE EL LOA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7658,7 +7658,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>133.23</v>
+        <v>115.51</v>
       </c>
     </row>
     <row r="112">
@@ -7729,7 +7729,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1173417-6-CM25</t>
+          <t>2258-17778-CM25</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>65.070.600-5</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7788,13 +7788,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>539.25</v>
+        <v>10030.88</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2258-17778-CM25</t>
+          <t>1173417-6-CM25</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>65.070.600-5</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>10030.88</v>
+        <v>539.25</v>
       </c>
     </row>
     <row r="115">
@@ -7924,7 +7924,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>778992-153-CM25</t>
+          <t>1423498-32-CM25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7964,17 +7964,17 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7983,13 +7983,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>308.14</v>
+        <v>84.19</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1423498-32-CM25</t>
+          <t>778992-153-CM25</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -8014,12 +8014,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -8029,17 +8029,17 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8048,7 +8048,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>84.19</v>
+        <v>308.14</v>
       </c>
     </row>
     <row r="118">
@@ -8314,7 +8314,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>922070-97-CM25</t>
+          <t>2258-18329-CM25</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>65.117.365-5</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8354,17 +8354,17 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>ABASTIBLE S.A.</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>91.806.000-6</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8373,13 +8373,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>291.79</v>
+        <v>379.93</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2258-18329-CM25</t>
+          <t>922070-97-CM25</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>65.117.365-5</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8419,17 +8419,17 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>ABASTIBLE S.A.</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>91.806.000-6</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -8438,13 +8438,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>379.93</v>
+        <v>291.79</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1079454-129-CM25</t>
+          <t>1423498-35-CM25</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8484,17 +8484,17 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -8503,13 +8503,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>12041.54</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1423498-35-CM25</t>
+          <t>1079454-129-CM25</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8549,17 +8549,17 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8568,7 +8568,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>83.7</v>
+        <v>12041.54</v>
       </c>
     </row>
     <row r="126">
@@ -8639,7 +8639,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>3274-128-CM25</t>
+          <t>778992-180-CM25</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8679,17 +8679,17 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -8698,13 +8698,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>318.48</v>
+        <v>767.08</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1171326-26-CM25</t>
+          <t>778992-171-CM25</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>61.926.300-6</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8744,17 +8744,17 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8763,13 +8763,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>106.65</v>
+        <v>310.32</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>778992-180-CM25</t>
+          <t>3274-128-CM25</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8794,12 +8794,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8809,17 +8809,17 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8828,7 +8828,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>767.08</v>
+        <v>318.48</v>
       </c>
     </row>
     <row r="130">
@@ -8899,7 +8899,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>778992-171-CM25</t>
+          <t>1171326-26-CM25</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8924,12 +8924,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>61.926.300-6</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8939,17 +8939,17 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8958,7 +8958,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>310.32</v>
+        <v>106.65</v>
       </c>
     </row>
     <row r="132">
@@ -9029,7 +9029,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2258-18551-CM25</t>
+          <t>838098-38-CM25</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -9049,17 +9049,17 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -9088,13 +9088,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>9328.299999999999</v>
+        <v>319.64</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>838098-38-CM25</t>
+          <t>2258-18551-CM25</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -9114,17 +9114,17 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -9153,7 +9153,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>319.64</v>
+        <v>9328.299999999999</v>
       </c>
     </row>
     <row r="135">
@@ -10004,7 +10004,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1423498-45-CM25</t>
+          <t>2430-175-CM25</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -10029,12 +10029,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -10044,17 +10044,17 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -10063,13 +10063,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>64.48</v>
+        <v>19253.26</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2430-175-CM25</t>
+          <t>1423498-45-CM25</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -10109,17 +10109,17 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -10128,13 +10128,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>19253.26</v>
+        <v>64.48</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2258-19025-CM25</t>
+          <t>2258-19048-CM25</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -10193,13 +10193,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>2841.69</v>
+        <v>7104.42</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2258-19048-CM25</t>
+          <t>2258-19025-CM25</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -10258,7 +10258,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>7104.42</v>
+        <v>2841.69</v>
       </c>
     </row>
     <row r="152">
@@ -10329,7 +10329,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1123-38-CM25</t>
+          <t>2605-36-CM25</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -10388,13 +10388,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>304.21</v>
+        <v>1053.65</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2605-36-CM25</t>
+          <t>1123-38-CM25</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -10419,12 +10419,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -10453,7 +10453,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>1053.65</v>
+        <v>304.21</v>
       </c>
     </row>
     <row r="155">
@@ -10719,7 +10719,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>3048-23-CM25</t>
+          <t>1346284-123-CM25</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10744,12 +10744,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>61.102.092-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10759,17 +10759,17 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>211.01</v>
+        <v>1840.53</v>
       </c>
     </row>
     <row r="160">
@@ -10849,7 +10849,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1346284-123-CM25</t>
+          <t>3048-23-CM25</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10874,12 +10874,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.102.092-9</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10889,17 +10889,17 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -10908,13 +10908,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>1840.53</v>
+        <v>211.01</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1410-724-CM25</t>
+          <t>1423498-50-CM25</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10934,17 +10934,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10973,13 +10973,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>1082.38</v>
+        <v>94.19</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1423498-50-CM25</t>
+          <t>1410-724-CM25</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10999,17 +10999,17 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -11038,7 +11038,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>94.19</v>
+        <v>1082.38</v>
       </c>
     </row>
     <row r="164">
@@ -11174,7 +11174,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2258-19660-CM25</t>
+          <t>2258-19746-CM25</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11233,13 +11233,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>1343.5</v>
+        <v>11445.34</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2258-19664-CM25</t>
+          <t>2258-19660-CM25</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11298,13 +11298,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>7230.64</v>
+        <v>1343.5</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2258-19746-CM25</t>
+          <t>2258-19664-CM25</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11363,7 +11363,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>11445.34</v>
+        <v>7230.64</v>
       </c>
     </row>
     <row r="169">
@@ -11824,7 +11824,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2258-20246-CM25</t>
+          <t>2258-20247-CM25</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11883,13 +11883,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>9688.77</v>
+        <v>16312.64</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2258-20245-CM25</t>
+          <t>2258-20243-CM25</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11948,13 +11948,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>8007.22</v>
+        <v>4201.92</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2258-20243-CM25</t>
+          <t>2258-20246-CM25</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -12013,13 +12013,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>4201.92</v>
+        <v>9688.77</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2258-20247-CM25</t>
+          <t>2258-20245-CM25</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -12078,7 +12078,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>16312.64</v>
+        <v>8007.22</v>
       </c>
     </row>
     <row r="180">
@@ -12994,7 +12994,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1410-845-CM25</t>
+          <t>1423498-55-CM25</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -13019,12 +13019,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -13034,17 +13034,17 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -13053,7 +13053,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>3910.91</v>
+        <v>87.45999999999999</v>
       </c>
     </row>
     <row r="195">
@@ -13124,7 +13124,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1423498-55-CM25</t>
+          <t>1410-845-CM25</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -13149,12 +13149,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -13164,17 +13164,17 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -13183,7 +13183,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>87.45999999999999</v>
+        <v>3910.91</v>
       </c>
     </row>
     <row r="197">
@@ -13774,7 +13774,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1410-913-CM25</t>
+          <t>2258-22401-CM25</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13799,12 +13799,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13814,17 +13814,17 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -13833,13 +13833,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>1182.18</v>
+        <v>12429.34</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2258-22399-CM25</t>
+          <t>1410-913-CM25</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13864,12 +13864,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13879,17 +13879,17 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -13898,13 +13898,13 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>13292.81</v>
+        <v>1182.18</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2258-22400-CM25</t>
+          <t>2258-22399-CM25</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13963,13 +13963,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>10573.92</v>
+        <v>13292.81</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2258-22401-CM25</t>
+          <t>2258-22400-CM25</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -14028,7 +14028,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>12429.34</v>
+        <v>10573.92</v>
       </c>
     </row>
     <row r="210">
@@ -14489,7 +14489,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1079454-592-CM25</t>
+          <t>1997-72-CM25</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -14509,17 +14509,17 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>60.511.023-1</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE EL LOA</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -14529,17 +14529,17 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -14548,13 +14548,13 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>467.81</v>
+        <v>218.97</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1997-72-CM25</t>
+          <t>1079454-592-CM25</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -14574,17 +14574,17 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>60.511.023-1</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE EL LOA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -14594,17 +14594,17 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -14613,7 +14613,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>218.97</v>
+        <v>467.81</v>
       </c>
     </row>
     <row r="219">
@@ -14944,7 +14944,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2258-23117-CM25</t>
+          <t>2258-23111-CM25</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -15003,13 +15003,13 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>7950.89</v>
+        <v>9210.49</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1410-1020-CM25</t>
+          <t>2258-23117-CM25</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -15034,12 +15034,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -15049,17 +15049,17 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -15068,13 +15068,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>1042.85</v>
+        <v>7950.89</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1057384-716-CM25</t>
+          <t>1410-1020-CM25</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -15099,12 +15099,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -15133,13 +15133,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>948.05</v>
+        <v>1042.85</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2258-23111-CM25</t>
+          <t>1057384-716-CM25</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -15164,12 +15164,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -15179,17 +15179,17 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -15198,7 +15198,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>9210.49</v>
+        <v>948.05</v>
       </c>
     </row>
     <row r="228">
@@ -15724,7 +15724,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>1233623-873-CM25</t>
+          <t>1410-1037-CM25</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -15749,12 +15749,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -15764,17 +15764,17 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -15783,7 +15783,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>112.2</v>
+        <v>2773.26</v>
       </c>
     </row>
     <row r="237">
@@ -15854,7 +15854,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>1410-1037-CM25</t>
+          <t>1233623-873-CM25</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -15879,12 +15879,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -15894,17 +15894,17 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -15913,13 +15913,13 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>2773.26</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2258-25863-CM25</t>
+          <t>2258-25861-CM25</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15978,13 +15978,13 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>5350.91</v>
+        <v>1486.99</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2258-25861-CM25</t>
+          <t>2258-25863-CM25</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -16043,7 +16043,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>1486.99</v>
+        <v>5350.91</v>
       </c>
     </row>
     <row r="241">
@@ -16114,7 +16114,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>707415-154-CM25</t>
+          <t>1423498-70-CM25</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -16134,17 +16134,17 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -16154,17 +16154,17 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -16173,13 +16173,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>1147.41</v>
+        <v>85.12</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1423498-70-CM25</t>
+          <t>707415-154-CM25</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -16199,17 +16199,17 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -16219,17 +16219,17 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -16238,13 +16238,13 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>85.12</v>
+        <v>1147.41</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>3048-38-CM25</t>
+          <t>1171326-63-CM25</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -16269,12 +16269,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>61.102.092-9</t>
+          <t>61.926.300-6</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -16303,13 +16303,13 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>106.28</v>
+        <v>63.58</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1171326-63-CM25</t>
+          <t>3048-38-CM25</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -16334,12 +16334,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>61.926.300-6</t>
+          <t>61.102.092-9</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -16368,13 +16368,13 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>63.58</v>
+        <v>106.28</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>778989-187-CM25</t>
+          <t>1346284-200-CM25</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -16399,12 +16399,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>65.081.190-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -16433,13 +16433,13 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>1141.11</v>
+        <v>3172.26</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1346284-200-CM25</t>
+          <t>778989-187-CM25</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -16464,12 +16464,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>65.081.190-9</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -16498,7 +16498,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>3172.26</v>
+        <v>1141.11</v>
       </c>
     </row>
     <row r="248">
@@ -16634,7 +16634,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2258-25921-CM25</t>
+          <t>2258-25924-CM25</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -16693,13 +16693,13 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>5430.19</v>
+        <v>6889.41</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2258-25924-CM25</t>
+          <t>2258-25921-CM25</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -16758,7 +16758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>6889.41</v>
+        <v>5430.19</v>
       </c>
     </row>
     <row r="252">
@@ -17934,7 +17934,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>1423498-80-CM25</t>
+          <t>2430-404-CM25</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -17959,12 +17959,12 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -17974,17 +17974,17 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -17993,13 +17993,13 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>82.88</v>
+        <v>19489.71</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2430-404-CM25</t>
+          <t>1423498-80-CM25</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -18024,12 +18024,12 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -18039,17 +18039,17 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -18058,7 +18058,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>19489.71</v>
+        <v>82.88</v>
       </c>
     </row>
     <row r="272">
@@ -19884,7 +19884,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>1410-83-CM26</t>
+          <t>1423498-25-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -19909,12 +19909,12 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -19924,17 +19924,17 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
@@ -19943,13 +19943,13 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>3028.72</v>
+        <v>86.17</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>1423498-25-CM26</t>
+          <t>1410-83-CM26</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -19974,12 +19974,12 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -19989,17 +19989,17 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
@@ -20008,13 +20008,13 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>86.17</v>
+        <v>3028.72</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2258-1269-CM26</t>
+          <t>2258-1270-CM26</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -20073,13 +20073,13 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>4373.28</v>
+        <v>2259.95</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2258-1270-CM26</t>
+          <t>2258-1269-CM26</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -20138,7 +20138,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>2259.95</v>
+        <v>4373.28</v>
       </c>
     </row>
     <row r="304">
@@ -20209,7 +20209,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2258-1423-CM26</t>
+          <t>3174-20-CM26</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -20234,12 +20234,12 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.102.045-7</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -20249,17 +20249,17 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
@@ -20268,13 +20268,13 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>5694.95</v>
+        <v>556.03</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>3174-20-CM26</t>
+          <t>2258-1423-CM26</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -20299,12 +20299,12 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>61.102.045-7</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -20314,17 +20314,17 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
@@ -20333,7 +20333,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>556.03</v>
+        <v>5694.95</v>
       </c>
     </row>
     <row r="307">
@@ -20404,7 +20404,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2122-18-CM26</t>
+          <t>2258-1470-CM26</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -20429,12 +20429,12 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -20463,13 +20463,13 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>209.24</v>
+        <v>3937.82</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2258-1470-CM26</t>
+          <t>2122-18-CM26</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -20494,12 +20494,12 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -20528,7 +20528,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>3937.82</v>
+        <v>209.24</v>
       </c>
     </row>
     <row r="310">
@@ -20664,7 +20664,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>1423498-33-CM26</t>
+          <t>2258-1802-CM26</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -20684,17 +20684,17 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -20704,17 +20704,17 @@
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
@@ -20723,13 +20723,13 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>83.33</v>
+        <v>4574.61</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2258-1802-CM26</t>
+          <t>1423498-33-CM26</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -20749,17 +20749,17 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -20769,17 +20769,17 @@
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
@@ -20788,7 +20788,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>4574.61</v>
+        <v>83.33</v>
       </c>
     </row>
     <row r="314">
@@ -21119,7 +21119,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>1079454-57-CM26</t>
+          <t>3274-66-CM26</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -21144,12 +21144,12 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -21159,17 +21159,17 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
@@ -21178,13 +21178,13 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>1276.83</v>
+        <v>1796.91</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>778992-46-CM26</t>
+          <t>769-142-CM26</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -21209,12 +21209,12 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -21224,17 +21224,17 @@
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
@@ -21243,13 +21243,13 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>1171.77</v>
+        <v>1677.73</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>769-142-CM26</t>
+          <t>778992-46-CM26</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -21274,12 +21274,12 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -21289,17 +21289,17 @@
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
@@ -21308,13 +21308,13 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>1677.73</v>
+        <v>1171.77</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>3274-66-CM26</t>
+          <t>1079454-57-CM26</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -21354,17 +21354,17 @@
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
@@ -21373,7 +21373,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>1796.91</v>
+        <v>1276.83</v>
       </c>
     </row>
     <row r="323">
@@ -21444,7 +21444,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2258-2013-CM26</t>
+          <t>778989-33-CM26</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -21469,12 +21469,12 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>65.081.190-9</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -21484,17 +21484,17 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
@@ -21503,13 +21503,13 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>3762.44</v>
+        <v>2091.45</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>778989-33-CM26</t>
+          <t>2258-2009-CM26</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -21534,12 +21534,12 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>65.081.190-9</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -21549,17 +21549,17 @@
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
@@ -21568,13 +21568,13 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>2091.45</v>
+        <v>1367.49</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2258-2009-CM26</t>
+          <t>2258-2013-CM26</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -21633,13 +21633,13 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>1367.49</v>
+        <v>3762.44</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>1013609-26-CM26</t>
+          <t>778992-47-CM26</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -21664,7 +21664,7 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>65.158.175-3</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
@@ -21679,17 +21679,17 @@
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
@@ -21698,13 +21698,13 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>1719.46</v>
+        <v>1288.95</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>778992-47-CM26</t>
+          <t>1013609-26-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -21729,7 +21729,7 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>65.158.175-3</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
@@ -21744,17 +21744,17 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
@@ -21763,7 +21763,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>1288.95</v>
+        <v>1719.46</v>
       </c>
     </row>
     <row r="329">
@@ -21834,7 +21834,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>1233623-59-CM26</t>
+          <t>1410-205-CM26</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -21859,12 +21859,12 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -21874,17 +21874,17 @@
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
@@ -21893,13 +21893,13 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>335.4</v>
+        <v>1040.09</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>1410-205-CM26</t>
+          <t>1233623-62-CM26</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -21924,12 +21924,12 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -21939,17 +21939,17 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
@@ -21958,13 +21958,13 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>1040.09</v>
+        <v>335.4</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>1233623-62-CM26</t>
+          <t>1233623-61-CM26</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -22029,7 +22029,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>1233623-61-CM26</t>
+          <t>1233623-60-CM26</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -22094,7 +22094,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>1233623-60-CM26</t>
+          <t>1233623-59-CM26</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -22159,7 +22159,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>1233623-58-CM26</t>
+          <t>1233623-56-CM26</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -22224,7 +22224,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>1233623-56-CM26</t>
+          <t>1233623-57-CM26</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -22289,7 +22289,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>1233623-55-CM26</t>
+          <t>1233623-53-CM26</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -22419,7 +22419,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>1233623-53-CM26</t>
+          <t>1233623-55-CM26</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -22484,7 +22484,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>1233623-52-CM26</t>
+          <t>1233623-58-CM26</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -22524,17 +22524,17 @@
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
@@ -22543,7 +22543,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>133.76</v>
+        <v>335.4</v>
       </c>
     </row>
     <row r="341">
@@ -22614,7 +22614,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>1233623-57-CM26</t>
+          <t>1233623-52-CM26</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -22654,17 +22654,17 @@
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
@@ -22673,7 +22673,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>335.4</v>
+        <v>133.76</v>
       </c>
     </row>
     <row r="343">
@@ -22744,7 +22744,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>3048-9-CM26</t>
+          <t>3048-8-CM26</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -22784,17 +22784,17 @@
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>415.1</v>
+        <v>117.3</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>3048-8-CM26</t>
+          <t>3048-9-CM26</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -22849,17 +22849,17 @@
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
@@ -22868,7 +22868,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>117.3</v>
+        <v>415.1</v>
       </c>
     </row>
     <row r="346">
@@ -23199,7 +23199,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2430-68-CM26</t>
+          <t>1171326-13-CM26</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -23224,12 +23224,12 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>61.926.300-6</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -23258,13 +23258,13 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>19340.81</v>
+        <v>44.96</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>1171326-13-CM26</t>
+          <t>2430-68-CM26</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -23289,12 +23289,12 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>61.926.300-6</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -23323,7 +23323,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>44.96</v>
+        <v>19340.81</v>
       </c>
     </row>
     <row r="353">
@@ -23459,7 +23459,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>1997-13-CM26</t>
+          <t>1346284-77-CM26</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -23479,17 +23479,17 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>60.511.023-1</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE EL LOA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -23499,17 +23499,17 @@
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K355" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
@@ -23518,13 +23518,13 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>181.79</v>
+        <v>3253.4</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>1346284-77-CM26</t>
+          <t>1997-13-CM26</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -23544,17 +23544,17 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>60.511.023-1</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE EL LOA</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -23564,17 +23564,17 @@
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K356" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
@@ -23583,13 +23583,13 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>3253.4</v>
+        <v>181.79</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>1080164-13-CM26</t>
+          <t>2258-2845-CM26</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -23614,12 +23614,12 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -23629,17 +23629,17 @@
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K357" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
@@ -23648,13 +23648,13 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>560.6</v>
+        <v>4122.66</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2258-2845-CM26</t>
+          <t>1080164-13-CM26</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -23679,12 +23679,12 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -23694,17 +23694,17 @@
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
@@ -23713,13 +23713,13 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>4122.66</v>
+        <v>560.6</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>1080164-16-CM26</t>
+          <t>1423498-56-CM26</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -23739,17 +23739,17 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -23778,13 +23778,13 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>463.13</v>
+        <v>104.65</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>1423498-56-CM26</t>
+          <t>1080164-16-CM26</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -23804,17 +23804,17 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -23843,13 +23843,13 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>104.65</v>
+        <v>463.13</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>1410-304-CM26</t>
+          <t>778992-73-CM26</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -23874,12 +23874,12 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -23908,13 +23908,13 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>1266.22</v>
+        <v>181.29</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>1997-15-CM26</t>
+          <t>1158-45-CM26</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -23939,12 +23939,12 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>60.511.023-1</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE EL LOA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -23973,13 +23973,13 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>230.7</v>
+        <v>2112.05</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>778992-73-CM26</t>
+          <t>1410-304-CM26</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -24004,12 +24004,12 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -24038,13 +24038,13 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>181.29</v>
+        <v>1266.22</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>1158-45-CM26</t>
+          <t>1997-15-CM26</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -24069,12 +24069,12 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.511.023-1</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE EL LOA</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -24103,7 +24103,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>2112.05</v>
+        <v>230.7</v>
       </c>
     </row>
     <row r="365">
@@ -24174,7 +24174,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>778989-65-CM26</t>
+          <t>2258-3139-CM26</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -24199,12 +24199,12 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>65.081.190-9</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -24233,13 +24233,13 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>234.16</v>
+        <v>1701.97</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2258-3139-CM26</t>
+          <t>2258-3140-CM26</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -24298,13 +24298,13 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>1701.97</v>
+        <v>9178.32</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2258-3140-CM26</t>
+          <t>778989-65-CM26</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -24329,12 +24329,12 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>65.081.190-9</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -24363,7 +24363,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>9178.32</v>
+        <v>234.16</v>
       </c>
     </row>
     <row r="369">
@@ -24629,7 +24629,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>707415-54-CM26</t>
+          <t>1079454-122-CM26</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -24654,12 +24654,12 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -24688,13 +24688,13 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>4021.6</v>
+        <v>13711.54</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>1079454-122-CM26</t>
+          <t>707415-54-CM26</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -24719,12 +24719,12 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -24753,7 +24753,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>13711.54</v>
+        <v>4021.6</v>
       </c>
     </row>
     <row r="375">
@@ -25279,7 +25279,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>1079454-143-CM26</t>
+          <t>778992-119-CM26</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -25299,17 +25299,17 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -25319,17 +25319,17 @@
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K383" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
@@ -25338,13 +25338,13 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>1010.73</v>
+        <v>1502.2</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>778992-119-CM26</t>
+          <t>1079454-143-CM26</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -25364,17 +25364,17 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -25384,17 +25384,17 @@
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K384" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L384" t="inlineStr">
@@ -25403,13 +25403,13 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>1502.2</v>
+        <v>1010.73</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2258-3883-CM26</t>
+          <t>2385-328-CM26</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -25429,17 +25429,17 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -25468,7 +25468,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>9676.77</v>
+        <v>1877.81</v>
       </c>
     </row>
     <row r="386">
@@ -25539,7 +25539,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2385-328-CM26</t>
+          <t>2258-3883-CM26</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -25559,17 +25559,17 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -25598,7 +25598,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>1877.81</v>
+        <v>9676.77</v>
       </c>
     </row>
     <row r="388">
@@ -25669,7 +25669,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>1233623-191-CM26</t>
+          <t>1013609-60-CM26</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -25694,12 +25694,12 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>65.158.175-3</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -25709,17 +25709,17 @@
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K389" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L389" t="inlineStr">
@@ -25728,13 +25728,13 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>278.67</v>
+        <v>2217.49</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>1013609-60-CM26</t>
+          <t>1233623-191-CM26</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -25759,12 +25759,12 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>65.158.175-3</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -25774,17 +25774,17 @@
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K390" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
@@ -25793,7 +25793,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>2217.49</v>
+        <v>278.67</v>
       </c>
     </row>
     <row r="391">
@@ -26124,7 +26124,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2258-4569-CM26</t>
+          <t>1775-33-CM26</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -26149,12 +26149,12 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>60.804.004-8</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -26183,7 +26183,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>13859.9</v>
+        <v>568.87</v>
       </c>
     </row>
     <row r="397">
@@ -26254,7 +26254,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>1775-33-CM26</t>
+          <t>2258-4569-CM26</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -26279,12 +26279,12 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>60.804.004-8</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -26313,7 +26313,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>568.87</v>
+        <v>13859.9</v>
       </c>
     </row>
     <row r="399">
@@ -27034,7 +27034,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>1346284-108-CM26</t>
+          <t>838098-29-CM26</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -27059,12 +27059,12 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -27074,17 +27074,17 @@
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K410" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L410" t="inlineStr">
@@ -27093,13 +27093,13 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>3331.34</v>
+        <v>674.3200000000001</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>838098-29-CM26</t>
+          <t>1346284-108-CM26</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -27124,12 +27124,12 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
@@ -27139,17 +27139,17 @@
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K411" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L411" t="inlineStr">
@@ -27158,7 +27158,7 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>674.3200000000001</v>
+        <v>3331.34</v>
       </c>
     </row>
     <row r="412">
@@ -27489,7 +27489,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>2258-5544-CM26</t>
+          <t>2258-5542-CM26</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -27548,13 +27548,13 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>6481.29</v>
+        <v>3503.57</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>2258-5542-CM26</t>
+          <t>778992-175-CM26</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -27579,12 +27579,12 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
@@ -27594,17 +27594,17 @@
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K418" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L418" t="inlineStr">
@@ -27613,13 +27613,13 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>3503.57</v>
+        <v>328.76</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>3174-127-CM26</t>
+          <t>1410-571-CM26</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -27644,12 +27644,12 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>61.102.045-7</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
@@ -27659,17 +27659,17 @@
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K419" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L419" t="inlineStr">
@@ -27678,13 +27678,13 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>649.83</v>
+        <v>3276.45</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>778992-175-CM26</t>
+          <t>3174-127-CM26</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -27709,12 +27709,12 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>61.102.045-7</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -27743,13 +27743,13 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>328.76</v>
+        <v>649.83</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>1410-571-CM26</t>
+          <t>2258-5544-CM26</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -27774,12 +27774,12 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -27808,7 +27808,7 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>3276.45</v>
+        <v>6481.29</v>
       </c>
     </row>
     <row r="422">
@@ -28984,7 +28984,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>778989-147-CM26</t>
+          <t>3048-21-CM26</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -29009,12 +29009,12 @@
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>65.081.190-9</t>
+          <t>61.102.092-9</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -29043,13 +29043,13 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>1439.22</v>
+        <v>316.98</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>3048-20-CM26</t>
+          <t>778989-147-CM26</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -29074,12 +29074,12 @@
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>61.102.092-9</t>
+          <t>65.081.190-9</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -29089,17 +29089,17 @@
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>GASCO GLP S A</t>
+          <t>EMPRESAS LIPIGAS S A</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
         <is>
-          <t>96.568.740-8</t>
+          <t>96.928.510-k</t>
         </is>
       </c>
       <c r="K441" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L441" t="inlineStr">
@@ -29108,13 +29108,13 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>128.14</v>
+        <v>1439.22</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>3048-21-CM26</t>
+          <t>3048-20-CM26</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -29154,17 +29154,17 @@
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>EMPRESAS LIPIGAS S A</t>
+          <t>GASCO GLP S A</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>96.928.510-k</t>
+          <t>96.568.740-8</t>
         </is>
       </c>
       <c r="K442" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L442" t="inlineStr">
@@ -29173,7 +29173,7 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>316.98</v>
+        <v>128.14</v>
       </c>
     </row>
     <row r="443">
@@ -29569,7 +29569,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>2258-6316-CM26</t>
+          <t>2258-6607-CM26</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -29628,13 +29628,13 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>8774.98</v>
+        <v>7580.92</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>2258-6606-CM26</t>
+          <t>2258-6316-CM26</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -29693,13 +29693,13 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>1134.63</v>
+        <v>8774.98</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>2258-6607-CM26</t>
+          <t>2258-6606-CM26</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -29758,7 +29758,7 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>7580.92</v>
+        <v>1134.63</v>
       </c>
     </row>
     <row r="452">
@@ -30759,7 +30759,7 @@
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F467" t="inlineStr">
@@ -30864,6 +30864,1176 @@
       </c>
       <c r="M468" s="2" t="n">
         <v>84.81999999999999</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>838098-47-CM26</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>73.923.800-5</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M469" s="2" t="n">
+        <v>1197.34</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>1171326-55-CM26</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>61.926.300-6</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M470" s="2" t="n">
+        <v>132.57</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>778992-325-CM26</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>61.953.000-4</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M471" s="2" t="n">
+        <v>166.09</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>1410-960-CM26</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>61.004.007-1</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M472" s="2" t="n">
+        <v>610.23</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>1171326-62-CM26</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>61.926.300-6</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M473" s="2" t="n">
+        <v>161.8</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2258-8044-CM26</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>61.606.201-8</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M474" s="2" t="n">
+        <v>9159.799999999999</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2258-7872-CM26</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>61.606.201-8</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M475" s="2" t="n">
+        <v>1142.71</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2258-7871-CM26</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>61.606.201-8</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M476" s="2" t="n">
+        <v>7212.15</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2258-7847-CM26</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>61.606.201-8</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M477" s="2" t="n">
+        <v>8477.17</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2258-7845-CM26</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>61.606.201-8</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M478" s="2" t="n">
+        <v>7474.6</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2258-7782-CM26</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>61.606.201-8</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M479" s="2" t="n">
+        <v>4550.51</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2258-7843-CM26</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>61.606.201-8</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M480" s="2" t="n">
+        <v>3212.4</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2258-7781-CM26</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>61.606.201-8</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M481" s="2" t="n">
+        <v>7450.28</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2258-7779-CM26</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>61.606.201-8</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M482" s="2" t="n">
+        <v>7198.92</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2258-7759-CM26</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>61.606.201-8</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M483" s="2" t="n">
+        <v>8041.2</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2258-7844-CM26</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>61.606.201-8</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>GASCO GLP S A</t>
+        </is>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>96.568.740-8</t>
+        </is>
+      </c>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M484" s="2" t="n">
+        <v>7668.82</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>1423498-185-CM26</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>62.000.890-7</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M485" s="2" t="n">
+        <v>97.3</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>778989-178-CM26</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>2239-1-LR25</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>65.081.190-9</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>EMPRESAS LIPIGAS S A</t>
+        </is>
+      </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>96.928.510-k</t>
+        </is>
+      </c>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M486" s="2" t="n">
+        <v>1436.73</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/gas-licuado-de-petroleo/antofagasta.xlsx
+++ b/docs/oc-regiones/gas-licuado-de-petroleo/antofagasta.xlsx
@@ -20749,7 +20749,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -21074,7 +21074,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
@@ -23024,7 +23024,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
@@ -23739,7 +23739,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
@@ -25039,7 +25039,7 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
@@ -25364,7 +25364,7 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
@@ -28289,7 +28289,7 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
@@ -28419,7 +28419,7 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
@@ -28484,7 +28484,7 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">

--- a/docs/oc-regiones/gas-licuado-de-petroleo/antofagasta.xlsx
+++ b/docs/oc-regiones/gas-licuado-de-petroleo/antofagasta.xlsx
@@ -31279,7 +31279,7 @@
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F475" t="inlineStr">
